--- a/07_ai-security-metrics-and-dashboarding/exercises/starter/kri_definitions.xlsx
+++ b/07_ai-security-metrics-and-dashboarding/exercises/starter/kri_definitions.xlsx
@@ -534,7 +534,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NorthBank — Portfolio KRI Exercise</t>
+          <t>UdaciBank — Portfolio KRI Exercise</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>COMPANY: NorthBank (digital-only fintech, 850 employees, US + UK)</t>
+          <t>COMPANY: UdaciBank (digital-only fintech, 850 employees, US + UK)</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  R-03: Anomalous refusal-rate spikes on the assistant indicate either policy drift or attempted misuse — both warrant investigationant indicate prompt-injection / abuse.</t>
+          <t xml:space="preserve">  R-03: Anomalous behavior on the assistant — including refusal-rate spikes and jailbreak-classifier hits — indicates either policy drift or attempted misuse and warrants investigation.</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Refusal rate — LLM customer-support assistant (Aurora Assistant)</t>
+          <t>Jailbreak-classifier hit rate — Aurora Assistant (LLM customer-support)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>R-03: Anomalous refusal-rate spikes (policy drift or attempted misuse)</t>
+          <t>R-03: Anomalous behavior on the assistant (refusal-rate spikes + jailbreak-classifier hits) — policy drift or attempted misuse</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Refusal rate (Aurora Assistant)</t>
+          <t>Jailbreak-classifier hit rate (Aurora Assistant)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>R-03: Anomalous refusal-rate spikes</t>
+          <t>R-03: Anomalous behavior on the assistant (refusal-rate spikes + jailbreak hits)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Refusal rate — Aurora Assistant</t>
+          <t>Jailbreak-classifier hit rate — Aurora Assistant</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>g ≤ 3% / a 3-7% / r &gt; 7%</t>
+          <t>g ≤ 0.05% / a 0.05-0.20% / r &gt; 0.20% (rolling 7-day)</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">

--- a/07_ai-security-metrics-and-dashboarding/exercises/starter/kri_definitions.xlsx
+++ b/07_ai-security-metrics-and-dashboarding/exercises/starter/kri_definitions.xlsx
@@ -844,32 +844,32 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the specific data source that emits this metric. Look at the KRI #1 / #2 worked examples in rows 2-3 (they cite specific files like fraud_predictions.csv or named feature snapshots), and check the Portfolio Inventory's 'Current Monitoring' column for the asset this KRI watches.]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — set green/amber/red threshold bands in the same format as KRI #1 (e.g., 'green ≤ 0.05 / amber 0.05–0.10 / red &gt; 0.10'). Anchor the bands to a plausible historical baseline for the asset's monitoring posture (see Portfolio Inventory).]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a measurement cadence (e.g., Daily rolling 7-day, Weekly, Monthly). Match the cadence to how often the underlying signal is emitted — compare to KRI #1 (Weekly) and KRI #2 (Monthly).]</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role that owns this KRI. The worked examples in rows 2-3 show titles like 'Fraud Model Owner' and 'Credit Model Owner'; pick the role whose remit matches the risk source in column C and the asset class.]</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write the escalation chain as &lt;Owner&gt; → &lt;AIRB / Risk Board&gt; → &lt;Senior leadership at red&gt;. Match the pattern of KRI #1 / #2 rows.]</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write one plain-English question a board member could ask to interpret this KRI, in the style of KRI #1 / #2 (e.g., 'Across all subgroups, what is the worst-case false-negative-rate gap on the fraud model?').]</t>
         </is>
       </c>
     </row>
@@ -889,32 +889,32 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the specific data source that emits this metric. Look at the KRI #1 / #2 worked examples in rows 2-3 (they cite specific files like fraud_predictions.csv or named feature snapshots), and check the Portfolio Inventory's 'Current Monitoring' column for the asset this KRI watches.]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — set green/amber/red threshold bands in the same format as KRI #1 (e.g., 'green ≤ 0.05 / amber 0.05–0.10 / red &gt; 0.10'). Anchor the bands to a plausible historical baseline for the asset's monitoring posture (see Portfolio Inventory).]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a measurement cadence (e.g., Daily rolling 7-day, Weekly, Monthly). Match the cadence to how often the underlying signal is emitted — compare to KRI #1 (Weekly) and KRI #2 (Monthly).]</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role that owns this KRI. The worked examples in rows 2-3 show titles like 'Fraud Model Owner' and 'Credit Model Owner'; pick the role whose remit matches the risk source in column C and the asset class.]</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write the escalation chain as &lt;Owner&gt; → &lt;AIRB / Risk Board&gt; → &lt;Senior leadership at red&gt;. Match the pattern of KRI #1 / #2 rows.]</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write one plain-English question a board member could ask to interpret this KRI, in the style of KRI #1 / #2 (e.g., 'Across all subgroups, what is the worst-case false-negative-rate gap on the fraud model?').]</t>
         </is>
       </c>
     </row>
@@ -934,32 +934,32 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the specific data source that emits this metric. Look at the KRI #1 / #2 worked examples in rows 2-3 (they cite specific files like fraud_predictions.csv or named feature snapshots), and check the Portfolio Inventory's 'Current Monitoring' column for the asset this KRI watches.]</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — set green/amber/red threshold bands in the same format as KRI #1 (e.g., 'green ≤ 0.05 / amber 0.05–0.10 / red &gt; 0.10'). Anchor the bands to a plausible historical baseline for the asset's monitoring posture (see Portfolio Inventory).]</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a measurement cadence (e.g., Daily rolling 7-day, Weekly, Monthly). Match the cadence to how often the underlying signal is emitted — compare to KRI #1 (Weekly) and KRI #2 (Monthly).]</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the role that owns this KRI. The worked examples in rows 2-3 show titles like 'Fraud Model Owner' and 'Credit Model Owner'; pick the role whose remit matches the risk source in column C and the asset class.]</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write the escalation chain as &lt;Owner&gt; → &lt;AIRB / Risk Board&gt; → &lt;Senior leadership at red&gt;. Match the pattern of KRI #1 / #2 rows.]</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write one plain-English question a board member could ask to interpret this KRI, in the style of KRI #1 / #2 (e.g., 'Across all subgroups, what is the worst-case false-negative-rate gap on the fraud model?').]</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the 1-2 Portfolio Inventory model IDs (M-01 … M-10) that this KRI is intended to detect risk on, with a short reason. Follow the format of row 2 / row 3 (e.g., 'M-01 FraudShield-v4 (primary); M-02 CreditDecision-v7 (secondary)'). The KRI Name in column B and Risk Register row in column C tell you which assets are in scope.]</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the 1-2 Portfolio Inventory model IDs (M-01 … M-10) that this KRI is intended to detect risk on, with a short reason. Follow the format of row 2 / row 3 (e.g., 'M-01 FraudShield-v4 (primary); M-02 CreditDecision-v7 (secondary)'). The KRI Name in column B and Risk Register row in column C tell you which assets are in scope.]</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the 1-2 Portfolio Inventory model IDs (M-01 … M-10) that this KRI is intended to detect risk on, with a short reason. Follow the format of row 2 / row 3 (e.g., 'M-01 FraudShield-v4 (primary); M-02 CreditDecision-v7 (secondary)'). The KRI Name in column B and Risk Register row in column C tell you which assets are in scope.]</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write the design-spec narrative for this KRI's panel. Describe the visualization (sparkline, bar gauge, time-series), how the amber/red threshold bands appear visually, and add a one-line note that the live pipe is wired in next sprint. Match the tone of KRI #1 / #2 narratives in rows 2-3, but note that columns C/D are '[design-spec]' here because the data pipe isn't live yet.]</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write the design-spec narrative for this KRI's panel. Describe the visualization (sparkline, bar gauge, time-series), how the amber/red threshold bands appear visually, and add a one-line note that the live pipe is wired in next sprint. Match the tone of KRI #1 / #2 narratives in rows 2-3, but note that columns C/D are '[design-spec]' here because the data pipe isn't live yet.]</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — write the design-spec narrative for this KRI's panel. Describe the visualization (sparkline, bar gauge, time-series), how the amber/red threshold bands appear visually, and add a one-line note that the live pipe is wired in next sprint. Match the tone of KRI #1 / #2 narratives in rows 2-3, but note that columns C/D are '[design-spec]' here because the data pipe isn't live yet.]</t>
         </is>
       </c>
     </row>

--- a/07_ai-security-metrics-and-dashboarding/exercises/starter/kri_definitions.xlsx
+++ b/07_ai-security-metrics-and-dashboarding/exercises/starter/kri_definitions.xlsx
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="C3" s="15" t="n">
-        <v>0.34</v>
+        <v>1.96</v>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>g ≤ 0.05% / a 0.05-0.20% / r &gt; 0.20% (rolling 7-day)</t>
+          <t>[Your response here — carry over the green/amber/red band you defined on the KRI Definitions sheet (E4).]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>g ≤ 0.1% / a 0.1-0.5% / r &gt; 0.5%</t>
+          <t>[Your response here — carry over the green/amber/red band you defined on the KRI Definitions sheet (E5).]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>g ≥ 90% / a 70-90% / r &lt; 70%</t>
+          <t>[Your response here — carry over the green/amber/red band you defined on the KRI Definitions sheet (E6).]</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
